--- a/data/trans_camb/IP07B_R-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP07B_R-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>12.89977089103381</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-10.16162662842942</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>11.60799963116661</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>8.571470579108119</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>12.24032482026692</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.5136571515862554</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>3.891423745458229</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-28.71248427944584</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1.074344263841264</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-8.590110403802614</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>5.599310083471444</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-11.7816851108427</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>21.62034668681337</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.716847716797806</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>21.36097486122728</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>21.65219882630534</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>19.09534020267569</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>10.72522880557079</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.1878879868752169</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.14800631629204</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.1699505813972879</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.1254933196618969</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1787181572251093</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.007499789501092037</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>0.05381157598328613</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.4043231177106598</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.01512612871640955</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.1205698501497999</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.07774012656952468</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1647145736616661</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.3451870536623229</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.1053040296663182</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.3461541123312632</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.3368756602507166</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.2984171305004747</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.1643988773437694</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>10.15707019238241</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-18.63236020556911</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>16.55849506137814</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.6650305449324323</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>13.36937481028528</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-10.55711331287932</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-1.177807223533913</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-34.9269949140112</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>5.546540292022327</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-13.75618457560165</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>6.113885097398793</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-23.34611772947228</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>20.07220799537089</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-3.617730906142267</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>27.81966218961793</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>13.12375529116037</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>20.55231803749891</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-0.4962190353109827</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>0.1395228781131612</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.2559439358676294</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.2432726927057057</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.009770439330238903</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1897651618644196</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.14984786836093</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.01477116436467366</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.4594306011077514</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0.0712942073202478</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.1843845916790122</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0.08088377234121498</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3213303366924545</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.2996789533078736</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>-0.05053968495409775</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.4542703429457587</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.2157248976814101</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.3100142918196146</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.008341965298286999</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>11.96758592871151</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-4.869807206296639</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>10.65063014937139</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-13.49260588889557</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>11.6395155600242</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-8.625418739818203</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>0.8017331242625926</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-16.93075106670284</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.7552656411790472</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-27.16464213847339</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>4.067021143633697</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-17.70202398853677</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>22.68032763357387</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>6.971134035573444</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>22.95268337756547</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.5466697986832371</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>19.88312385735217</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.5141770342155001</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>0.164380109607875</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.06688896550304084</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.1326349801874611</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.1680268199770798</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.1528804613424215</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.1132914844621104</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>0.01330707852404193</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.2233839672647627</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0.0162487154387973</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.3199484454098031</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.05162339410669921</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.2241086847732121</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.3465973294378487</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.1039044071353406</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.331328891705889</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.004427657898227942</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.2806799734003774</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.006570018696680422</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-3.523840892271579</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-22.30282916139724</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>14.95276718230146</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-9.525820017945675</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>5.955868895958016</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-15.50193086087576</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-18.63645224937519</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-38.89901291531586</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-2.623157234101109</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-28.01216227837616</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-4.891470576318508</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-28.12148885700841</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>12.31440891010233</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-4.294627417065142</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>30.15108662482973</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>8.1445007728343</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>19.03003804665888</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-2.32274597635799</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.04330846476320589</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.2741046830390582</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.2135894987293142</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.1360694711429008</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.07919058709206503</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.2061171975706978</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.2126703149102707</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.4496902637402083</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.02535195953254407</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.3642046048713162</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.05583249264655673</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.3520686863437706</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.168448755377886</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>-0.06197239279340239</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.510923800800183</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.130329840748419</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.2762768832472847</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>-0.03491861865771807</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>9.898077817572993</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-12.0059684301536</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>13.04438142980542</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-2.988079619481865</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>11.44572465772158</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-8.155681798297254</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>4.759310406953463</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-20.84370077981994</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>7.511786989074622</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-10.64244359320784</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>7.721406549963166</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-14.30377637292834</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>15.72267553116908</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-4.652386004614619</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>18.76582028265134</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>4.258542715844832</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>15.75849950542086</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-2.687870385290252</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>0.1371295910108346</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.1663326527493038</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.183896830662861</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.04212529162444151</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.1598999507776817</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.1139371387224828</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>0.06346220144396154</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.283081890090004</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0.100773453111333</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.1435876215942568</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>0.1054465352126456</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.1967710987729804</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.2300660712002563</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>-0.06669530176793123</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.2828484423817818</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.06126586918637781</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.2289658578018768</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.03867983049618734</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
